--- a/analysis/metrics_results.xlsx
+++ b/analysis/metrics_results.xlsx
@@ -688,19 +688,19 @@
         </is>
       </c>
       <c r="C5" s="4" t="n">
-        <v>121.093</v>
+        <v>131.519</v>
       </c>
       <c r="D5" s="4" t="n">
-        <v>1.9558</v>
+        <v>1.4229</v>
       </c>
       <c r="E5" s="5" t="n">
-        <v>0.19558</v>
+        <v>0.14229</v>
       </c>
       <c r="F5" s="5" t="n">
-        <v>0.120876</v>
+        <v>0.0491206</v>
       </c>
       <c r="G5" s="5" t="n">
-        <v>0.347673</v>
+        <v>0.221632</v>
       </c>
     </row>
     <row r="6" ht="20" customHeight="1">
@@ -710,19 +710,19 @@
         </is>
       </c>
       <c r="C6" s="4" t="n">
-        <v>53.5234</v>
+        <v>67.43519999999999</v>
       </c>
       <c r="D6" s="4" t="n">
-        <v>0.7752</v>
+        <v>0.8053</v>
       </c>
       <c r="E6" s="5" t="n">
-        <v>0.07752000000000001</v>
+        <v>0.08053</v>
       </c>
       <c r="F6" s="5" t="n">
-        <v>0.00501665</v>
+        <v>0.0304619</v>
       </c>
       <c r="G6" s="5" t="n">
-        <v>0.0708283</v>
+        <v>0.174533</v>
       </c>
     </row>
     <row r="7" ht="20" customHeight="1">
@@ -732,19 +732,19 @@
         </is>
       </c>
       <c r="C7" s="4" t="n">
-        <v>318.009</v>
+        <v>337.732</v>
       </c>
       <c r="D7" s="4" t="n">
-        <v>2.5263</v>
+        <v>2.8585</v>
       </c>
       <c r="E7" s="5" t="n">
-        <v>0.25263</v>
+        <v>0.28585</v>
       </c>
       <c r="F7" s="5" t="n">
-        <v>0.156003</v>
+        <v>0.122763</v>
       </c>
       <c r="G7" s="5" t="n">
-        <v>0.394972</v>
+        <v>0.350375</v>
       </c>
     </row>
     <row r="8" ht="20" customHeight="1">
@@ -754,19 +754,19 @@
         </is>
       </c>
       <c r="C8" s="4" t="n">
-        <v>278.26</v>
+        <v>272.243</v>
       </c>
       <c r="D8" s="4" t="n">
-        <v>3.0621</v>
+        <v>2.4533</v>
       </c>
       <c r="E8" s="5" t="n">
-        <v>0.30621</v>
+        <v>0.24533</v>
       </c>
       <c r="F8" s="5" t="n">
-        <v>0.740042</v>
+        <v>0.230924</v>
       </c>
       <c r="G8" s="5" t="n">
-        <v>0.860257</v>
+        <v>0.480546</v>
       </c>
     </row>
     <row r="9"/>
